--- a/analysis/TEST/CBATCH.v2.0.0_1.xlsx
+++ b/analysis/TEST/CBATCH.v2.0.0_1.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE577FDE-DAFE-7847-8DC0-BCA50DAC5B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF68F1E-301C-5844-8A25-EE8B03FD627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2300" yWindow="1740" windowWidth="23220" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="Plate" sheetId="2" r:id="rId2"/>
+    <sheet name="Sample IDs" sheetId="2" r:id="rId2"/>
     <sheet name="Comments" sheetId="3" r:id="rId3"/>
     <sheet name="Lists" sheetId="4" r:id="rId4"/>
   </sheets>
